--- a/Global Arriendos/informe Global ARRIENDOS_cor.xlsx
+++ b/Global Arriendos/informe Global ARRIENDOS_cor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\Portada Inmobiliaria\Inmuebles_Arrendados\Global Arriendos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDEF6FEE-7CED-4540-B241-D6BC6EBAACA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B539AF0-ABB9-4D7D-B5C8-0E13F9F1CB36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8964" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="COLORES " sheetId="1" r:id="rId1"/>
@@ -7287,64 +7287,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="32" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="32" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="33" fillId="21" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -7444,6 +7386,64 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="19" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="27" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="27" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="27" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -11617,7 +11617,7 @@
       <c r="A73" s="232" t="s">
         <v>20</v>
       </c>
-      <c r="B73" s="718" t="s">
+      <c r="B73" s="686" t="s">
         <v>43</v>
       </c>
       <c r="C73" s="231" t="s">
@@ -12939,10 +12939,12 @@
     <col min="5" max="6" width="14.21875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.5546875" customWidth="1"/>
     <col min="8" max="8" width="11.88671875" customWidth="1"/>
-    <col min="9" max="9" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="0" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="0.109375" customWidth="1"/>
-    <col min="15" max="15" width="16.109375" customWidth="1"/>
+    <col min="9" max="10" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="49.2" x14ac:dyDescent="0.85">
@@ -12985,7 +12987,7 @@
         <v>9</v>
       </c>
       <c r="L2" s="292" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="M2" s="292" t="s">
         <v>11</v>
@@ -13407,10 +13409,10 @@
       <c r="I1" s="24"/>
     </row>
     <row r="2" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="701" t="s">
+      <c r="A2" s="743" t="s">
         <v>367</v>
       </c>
-      <c r="B2" s="702"/>
+      <c r="B2" s="744"/>
       <c r="C2" s="238"/>
       <c r="D2" s="238"/>
       <c r="E2" s="238"/>
@@ -13748,7 +13750,7 @@
       <c r="G14" s="573">
         <v>30197400</v>
       </c>
-      <c r="H14" s="744">
+      <c r="H14" s="712">
         <f t="shared" si="0"/>
         <v>159656400</v>
       </c>
@@ -13776,7 +13778,7 @@
       <c r="G15" s="646">
         <v>20130000</v>
       </c>
-      <c r="H15" s="745">
+      <c r="H15" s="713">
         <f t="shared" si="0"/>
         <v>139486000</v>
       </c>
@@ -13806,11 +13808,11 @@
         <f t="shared" si="1"/>
         <v>105061000</v>
       </c>
-      <c r="G16" s="741">
+      <c r="G16" s="709">
         <f t="shared" si="1"/>
         <v>294297400</v>
       </c>
-      <c r="H16" s="746"/>
+      <c r="H16" s="714"/>
       <c r="I16" s="24"/>
     </row>
     <row r="17" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -13837,22 +13839,22 @@
         <f t="shared" si="2"/>
         <v>8755083.333333334</v>
       </c>
-      <c r="G17" s="742">
+      <c r="G17" s="710">
         <f t="shared" si="2"/>
         <v>24524783.333333332</v>
       </c>
-      <c r="H17" s="747">
+      <c r="H17" s="715">
         <f>SUM(H4:H16)</f>
         <v>1638991335</v>
       </c>
-      <c r="I17" s="735"/>
-      <c r="J17" s="735"/>
-      <c r="K17" s="735"/>
-      <c r="L17" s="735"/>
-      <c r="M17" s="735"/>
-      <c r="N17" s="735"/>
-      <c r="O17" s="735"/>
-      <c r="P17" s="735"/>
+      <c r="I17" s="703"/>
+      <c r="J17" s="703"/>
+      <c r="K17" s="703"/>
+      <c r="L17" s="703"/>
+      <c r="M17" s="703"/>
+      <c r="N17" s="703"/>
+      <c r="O17" s="703"/>
+      <c r="P17" s="703"/>
       <c r="Q17" s="349"/>
     </row>
     <row r="18" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
@@ -13864,14 +13866,14 @@
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="347"/>
-      <c r="I18" s="736"/>
-      <c r="J18" s="736"/>
-      <c r="K18" s="736"/>
-      <c r="L18" s="736"/>
-      <c r="M18" s="736"/>
-      <c r="N18" s="736"/>
-      <c r="O18" s="736"/>
-      <c r="P18" s="735"/>
+      <c r="I18" s="704"/>
+      <c r="J18" s="704"/>
+      <c r="K18" s="704"/>
+      <c r="L18" s="704"/>
+      <c r="M18" s="704"/>
+      <c r="N18" s="704"/>
+      <c r="O18" s="704"/>
+      <c r="P18" s="703"/>
       <c r="Q18" s="349"/>
     </row>
     <row r="19" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
@@ -13883,35 +13885,35 @@
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="347"/>
-      <c r="I19" s="736"/>
-      <c r="J19" s="736"/>
-      <c r="K19" s="736"/>
-      <c r="L19" s="736"/>
-      <c r="M19" s="736"/>
-      <c r="N19" s="736"/>
-      <c r="O19" s="736"/>
-      <c r="P19" s="735"/>
+      <c r="I19" s="704"/>
+      <c r="J19" s="704"/>
+      <c r="K19" s="704"/>
+      <c r="L19" s="704"/>
+      <c r="M19" s="704"/>
+      <c r="N19" s="704"/>
+      <c r="O19" s="704"/>
+      <c r="P19" s="703"/>
       <c r="Q19" s="349"/>
     </row>
     <row r="20" spans="1:17" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A20" s="700" t="s">
+      <c r="A20" s="742" t="s">
         <v>378</v>
       </c>
-      <c r="B20" s="700"/>
-      <c r="C20" s="700"/>
+      <c r="B20" s="742"/>
+      <c r="C20" s="742"/>
       <c r="D20" s="238"/>
       <c r="E20" s="238"/>
       <c r="F20" s="238"/>
       <c r="G20" s="238"/>
-      <c r="H20" s="748"/>
-      <c r="I20" s="737"/>
-      <c r="J20" s="737"/>
-      <c r="K20" s="737"/>
-      <c r="L20" s="737"/>
-      <c r="M20" s="737"/>
-      <c r="N20" s="737"/>
-      <c r="O20" s="738"/>
-      <c r="P20" s="735"/>
+      <c r="H20" s="716"/>
+      <c r="I20" s="705"/>
+      <c r="J20" s="705"/>
+      <c r="K20" s="705"/>
+      <c r="L20" s="705"/>
+      <c r="M20" s="705"/>
+      <c r="N20" s="705"/>
+      <c r="O20" s="706"/>
+      <c r="P20" s="703"/>
       <c r="Q20" s="349"/>
     </row>
     <row r="21" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
@@ -13933,20 +13935,20 @@
       <c r="F21" s="174" t="s">
         <v>383</v>
       </c>
-      <c r="G21" s="743" t="s">
+      <c r="G21" s="711" t="s">
         <v>384</v>
       </c>
-      <c r="H21" s="749" t="s">
+      <c r="H21" s="717" t="s">
         <v>370</v>
       </c>
-      <c r="I21" s="739"/>
-      <c r="J21" s="739"/>
-      <c r="K21" s="739"/>
-      <c r="L21" s="740"/>
-      <c r="M21" s="739"/>
-      <c r="N21" s="739"/>
-      <c r="O21" s="735"/>
-      <c r="P21" s="735"/>
+      <c r="I21" s="707"/>
+      <c r="J21" s="707"/>
+      <c r="K21" s="707"/>
+      <c r="L21" s="708"/>
+      <c r="M21" s="707"/>
+      <c r="N21" s="707"/>
+      <c r="O21" s="703"/>
+      <c r="P21" s="703"/>
       <c r="Q21" s="349"/>
     </row>
     <row r="22" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
@@ -13971,18 +13973,18 @@
       <c r="G22" s="646">
         <v>41090000</v>
       </c>
-      <c r="H22" s="731">
+      <c r="H22" s="699">
         <f t="shared" ref="H22:H24" si="3">SUM(B22:G22)</f>
         <v>191750000</v>
       </c>
-      <c r="I22" s="739"/>
-      <c r="J22" s="739"/>
-      <c r="K22" s="739"/>
-      <c r="L22" s="739"/>
-      <c r="M22" s="739"/>
-      <c r="N22" s="739"/>
-      <c r="O22" s="735"/>
-      <c r="P22" s="735"/>
+      <c r="I22" s="707"/>
+      <c r="J22" s="707"/>
+      <c r="K22" s="707"/>
+      <c r="L22" s="707"/>
+      <c r="M22" s="707"/>
+      <c r="N22" s="707"/>
+      <c r="O22" s="703"/>
+      <c r="P22" s="703"/>
       <c r="Q22" s="349"/>
     </row>
     <row r="23" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
@@ -14364,11 +14366,11 @@
     <row r="37" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="38" spans="1:8" ht="2.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="39" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A39" s="697" t="s">
+      <c r="A39" s="739" t="s">
         <v>385</v>
       </c>
-      <c r="B39" s="698"/>
-      <c r="C39" s="699"/>
+      <c r="B39" s="740"/>
+      <c r="C39" s="741"/>
       <c r="D39" s="238"/>
       <c r="E39" s="238"/>
       <c r="F39" s="238"/>
@@ -14594,16 +14596,16 @@
       <c r="A48" s="656" t="s">
         <v>372</v>
       </c>
-      <c r="B48" s="720">
+      <c r="B48" s="688">
         <v>44010000</v>
       </c>
-      <c r="C48" s="721">
+      <c r="C48" s="689">
         <v>1700500</v>
       </c>
-      <c r="D48" s="722">
+      <c r="D48" s="690">
         <v>19460000</v>
       </c>
-      <c r="E48" s="723">
+      <c r="E48" s="691">
         <v>11030000</v>
       </c>
       <c r="F48" s="654">
@@ -14612,7 +14614,7 @@
       <c r="G48" s="636">
         <v>27620000</v>
       </c>
-      <c r="H48" s="724">
+      <c r="H48" s="692">
         <f t="shared" si="8"/>
         <v>110830500</v>
       </c>
@@ -14621,25 +14623,25 @@
       <c r="A49" s="658" t="s">
         <v>373</v>
       </c>
-      <c r="B49" s="725">
+      <c r="B49" s="693">
         <v>60045000</v>
       </c>
-      <c r="C49" s="725">
+      <c r="C49" s="693">
         <v>31960980</v>
       </c>
-      <c r="D49" s="726">
+      <c r="D49" s="694">
         <v>18400000</v>
       </c>
-      <c r="E49" s="725">
+      <c r="E49" s="693">
         <v>36650000</v>
       </c>
-      <c r="F49" s="726">
+      <c r="F49" s="694">
         <v>24490000</v>
       </c>
-      <c r="G49" s="725">
+      <c r="G49" s="693">
         <v>41920000</v>
       </c>
-      <c r="H49" s="727">
+      <c r="H49" s="695">
         <f t="shared" si="8"/>
         <v>213465980</v>
       </c>
@@ -14648,25 +14650,25 @@
       <c r="A50" s="658" t="s">
         <v>374</v>
       </c>
-      <c r="B50" s="728">
+      <c r="B50" s="696">
         <v>29320000</v>
       </c>
-      <c r="C50" s="725">
+      <c r="C50" s="693">
         <v>30350980</v>
       </c>
-      <c r="D50" s="726">
+      <c r="D50" s="694">
         <v>5200000</v>
       </c>
-      <c r="E50" s="726">
+      <c r="E50" s="694">
         <v>13280000</v>
       </c>
-      <c r="F50" s="728">
+      <c r="F50" s="696">
         <v>18820000</v>
       </c>
-      <c r="G50" s="725">
+      <c r="G50" s="693">
         <v>29050000</v>
       </c>
-      <c r="H50" s="727">
+      <c r="H50" s="695">
         <f t="shared" si="8"/>
         <v>126020980</v>
       </c>
@@ -14675,25 +14677,25 @@
       <c r="A51" s="658" t="s">
         <v>375</v>
       </c>
-      <c r="B51" s="725">
+      <c r="B51" s="693">
         <v>60410000</v>
       </c>
-      <c r="C51" s="725">
+      <c r="C51" s="693">
         <v>37440000</v>
       </c>
-      <c r="D51" s="725">
+      <c r="D51" s="693">
         <v>32750000</v>
       </c>
-      <c r="E51" s="726">
+      <c r="E51" s="694">
         <v>29333144</v>
       </c>
-      <c r="F51" s="726">
+      <c r="F51" s="694">
         <v>14080000</v>
       </c>
-      <c r="G51" s="725">
+      <c r="G51" s="693">
         <v>35100000</v>
       </c>
-      <c r="H51" s="727">
+      <c r="H51" s="695">
         <f t="shared" si="8"/>
         <v>209113144</v>
       </c>
@@ -14705,43 +14707,43 @@
       <c r="B52" s="605"/>
       <c r="C52" s="605"/>
       <c r="D52" s="605"/>
-      <c r="E52" s="725"/>
-      <c r="F52" s="729"/>
+      <c r="E52" s="693"/>
+      <c r="F52" s="697"/>
       <c r="G52" s="605"/>
-      <c r="H52" s="727"/>
+      <c r="H52" s="695"/>
     </row>
     <row r="53" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="730" t="s">
+      <c r="A53" s="698" t="s">
         <v>13</v>
       </c>
-      <c r="B53" s="731">
+      <c r="B53" s="699">
         <f>SUM(B41:B51)</f>
         <v>427308350</v>
       </c>
-      <c r="C53" s="731">
+      <c r="C53" s="699">
         <f>SUM(C41:C51)</f>
         <v>61453783220</v>
       </c>
-      <c r="D53" s="731">
+      <c r="D53" s="699">
         <f>SUM(D41:D51)</f>
         <v>153706680</v>
       </c>
-      <c r="E53" s="732">
+      <c r="E53" s="700">
         <f>SUM(E41:E52)</f>
         <v>223494144</v>
       </c>
-      <c r="F53" s="732">
+      <c r="F53" s="700">
         <f>SUM(F41:F52)</f>
         <v>156534804</v>
       </c>
-      <c r="G53" s="732">
+      <c r="G53" s="700">
         <f>SUM(G41:G51)</f>
         <v>318156000</v>
       </c>
-      <c r="H53" s="733"/>
+      <c r="H53" s="701"/>
     </row>
     <row r="54" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="734" t="s">
+      <c r="A54" s="702" t="s">
         <v>389</v>
       </c>
       <c r="B54" s="605">
@@ -14768,7 +14770,7 @@
       <c r="H54" s="348"/>
     </row>
     <row r="55" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="734" t="s">
+      <c r="A55" s="702" t="s">
         <v>390</v>
       </c>
       <c r="B55" s="605">
@@ -14795,15 +14797,15 @@
       <c r="H55" s="348"/>
     </row>
     <row r="58" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="703" t="s">
+      <c r="A58" s="745" t="s">
         <v>391</v>
       </c>
-      <c r="B58" s="704"/>
-      <c r="C58" s="704"/>
-      <c r="D58" s="704"/>
-      <c r="E58" s="704"/>
-      <c r="F58" s="704"/>
-      <c r="G58" s="705"/>
+      <c r="B58" s="746"/>
+      <c r="C58" s="746"/>
+      <c r="D58" s="746"/>
+      <c r="E58" s="746"/>
+      <c r="F58" s="746"/>
+      <c r="G58" s="747"/>
     </row>
     <row r="59" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="225" t="s">
@@ -15228,15 +15230,15 @@
     </row>
     <row r="72" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="73" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="706" t="s">
+      <c r="A73" s="748" t="s">
         <v>392</v>
       </c>
-      <c r="B73" s="707"/>
-      <c r="C73" s="707"/>
-      <c r="D73" s="707"/>
-      <c r="E73" s="707"/>
-      <c r="F73" s="707"/>
-      <c r="G73" s="707"/>
+      <c r="B73" s="749"/>
+      <c r="C73" s="749"/>
+      <c r="D73" s="749"/>
+      <c r="E73" s="749"/>
+      <c r="F73" s="749"/>
+      <c r="G73" s="749"/>
       <c r="H73" s="250"/>
       <c r="I73" s="671"/>
       <c r="J73" s="673"/>
@@ -17951,7 +17953,7 @@
       <c r="B53" s="208" t="s">
         <v>104</v>
       </c>
-      <c r="C53" s="716" t="s">
+      <c r="C53" s="684" t="s">
         <v>43</v>
       </c>
       <c r="D53" s="209"/>
@@ -18511,7 +18513,7 @@
       <c r="A69" s="232" t="s">
         <v>20</v>
       </c>
-      <c r="B69" s="717" t="s">
+      <c r="B69" s="685" t="s">
         <v>43</v>
       </c>
       <c r="C69" s="231" t="s">
@@ -18870,13 +18872,13 @@
       <c r="B79" s="263" t="s">
         <v>43</v>
       </c>
-      <c r="C79" s="713" t="s">
+      <c r="C79" s="681" t="s">
         <v>1</v>
       </c>
-      <c r="D79" s="713" t="s">
+      <c r="D79" s="681" t="s">
         <v>2</v>
       </c>
-      <c r="E79" s="712" t="s">
+      <c r="E79" s="680" t="s">
         <v>3</v>
       </c>
       <c r="F79" s="184" t="s">
@@ -18906,7 +18908,7 @@
       <c r="N79" s="263" t="s">
         <v>12</v>
       </c>
-      <c r="O79" s="708" t="s">
+      <c r="O79" s="676" t="s">
         <v>13</v>
       </c>
       <c r="P79" s="609" t="s">
@@ -18917,10 +18919,10 @@
       <c r="A80" s="272" t="s">
         <v>110</v>
       </c>
-      <c r="B80" s="710">
+      <c r="B80" s="678">
         <v>45000000</v>
       </c>
-      <c r="C80" s="714">
+      <c r="C80" s="682">
         <v>29750000</v>
       </c>
       <c r="D80" s="458">
@@ -18969,13 +18971,13 @@
       <c r="A81" s="163" t="s">
         <v>89</v>
       </c>
-      <c r="B81" s="711">
+      <c r="B81" s="679">
         <v>13000000</v>
       </c>
-      <c r="C81" s="715">
+      <c r="C81" s="683">
         <v>13600000</v>
       </c>
-      <c r="D81" s="715">
+      <c r="D81" s="683">
         <v>12700000</v>
       </c>
       <c r="E81" s="530">
@@ -21740,7 +21742,7 @@
       <c r="B35" s="350">
         <v>150000000</v>
       </c>
-      <c r="C35" s="709">
+      <c r="C35" s="677">
         <v>10200000</v>
       </c>
       <c r="D35" s="423">
@@ -22363,7 +22365,7 @@
       <c r="A51" s="232" t="s">
         <v>20</v>
       </c>
-      <c r="B51" s="717" t="s">
+      <c r="B51" s="685" t="s">
         <v>43</v>
       </c>
       <c r="C51" s="189"/>
@@ -24950,7 +24952,7 @@
       <c r="C50" s="424">
         <v>12325000</v>
       </c>
-      <c r="D50" s="719">
+      <c r="D50" s="687">
         <v>15250000</v>
       </c>
       <c r="E50" s="424">
@@ -30181,17 +30183,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="A1" s="695" t="s">
+      <c r="A1" s="720" t="s">
         <v>275</v>
       </c>
-      <c r="B1" s="694"/>
-      <c r="C1" s="694"/>
-      <c r="D1" s="694"/>
-      <c r="E1" s="694"/>
-      <c r="F1" s="694"/>
-      <c r="G1" s="694"/>
-      <c r="H1" s="694"/>
-      <c r="I1" s="694"/>
+      <c r="B1" s="721"/>
+      <c r="C1" s="721"/>
+      <c r="D1" s="721"/>
+      <c r="E1" s="721"/>
+      <c r="F1" s="721"/>
+      <c r="G1" s="721"/>
+      <c r="H1" s="721"/>
+      <c r="I1" s="721"/>
       <c r="J1" s="24"/>
     </row>
     <row r="2" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
@@ -30207,52 +30209,52 @@
       <c r="J2" s="24"/>
     </row>
     <row r="3" spans="1:30" ht="21" x14ac:dyDescent="0.4">
-      <c r="A3" s="687" t="s">
+      <c r="A3" s="724" t="s">
         <v>276</v>
       </c>
-      <c r="B3" s="685"/>
-      <c r="C3" s="686"/>
-      <c r="D3" s="688" t="s">
+      <c r="B3" s="725"/>
+      <c r="C3" s="723"/>
+      <c r="D3" s="722" t="s">
         <v>277</v>
       </c>
-      <c r="E3" s="686"/>
+      <c r="E3" s="723"/>
       <c r="F3" s="24"/>
-      <c r="G3" s="687" t="s">
+      <c r="G3" s="724" t="s">
         <v>278</v>
       </c>
-      <c r="H3" s="685"/>
-      <c r="I3" s="686"/>
-      <c r="J3" s="688" t="s">
+      <c r="H3" s="725"/>
+      <c r="I3" s="723"/>
+      <c r="J3" s="722" t="s">
         <v>279</v>
       </c>
-      <c r="K3" s="686"/>
-      <c r="M3" s="678" t="s">
+      <c r="K3" s="723"/>
+      <c r="M3" s="726" t="s">
         <v>280</v>
       </c>
-      <c r="N3" s="679"/>
-      <c r="O3" s="677"/>
-      <c r="P3" s="678" t="s">
+      <c r="N3" s="727"/>
+      <c r="O3" s="719"/>
+      <c r="P3" s="726" t="s">
         <v>281</v>
       </c>
-      <c r="Q3" s="677"/>
-      <c r="S3" s="678" t="s">
+      <c r="Q3" s="719"/>
+      <c r="S3" s="726" t="s">
         <v>282</v>
       </c>
-      <c r="T3" s="679"/>
-      <c r="U3" s="677"/>
-      <c r="V3" s="678" t="s">
+      <c r="T3" s="727"/>
+      <c r="U3" s="719"/>
+      <c r="V3" s="726" t="s">
         <v>283</v>
       </c>
-      <c r="W3" s="677"/>
-      <c r="Y3" s="678" t="s">
+      <c r="W3" s="719"/>
+      <c r="Y3" s="726" t="s">
         <v>284</v>
       </c>
-      <c r="Z3" s="679"/>
-      <c r="AA3" s="677"/>
-      <c r="AB3" s="678" t="s">
+      <c r="Z3" s="727"/>
+      <c r="AA3" s="719"/>
+      <c r="AB3" s="726" t="s">
         <v>285</v>
       </c>
-      <c r="AC3" s="677"/>
+      <c r="AC3" s="719"/>
     </row>
     <row r="4" spans="1:30" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" s="54" t="s">
@@ -30747,52 +30749,52 @@
       <c r="F12" s="24"/>
     </row>
     <row r="13" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A13" s="691" t="s">
+      <c r="A13" s="734" t="s">
         <v>292</v>
       </c>
-      <c r="B13" s="677"/>
+      <c r="B13" s="719"/>
       <c r="C13" s="24"/>
-      <c r="D13" s="692" t="s">
+      <c r="D13" s="735" t="s">
         <v>293</v>
       </c>
-      <c r="E13" s="686"/>
+      <c r="E13" s="723"/>
       <c r="F13" s="24"/>
-      <c r="G13" s="691" t="s">
+      <c r="G13" s="734" t="s">
         <v>294</v>
       </c>
-      <c r="H13" s="677"/>
+      <c r="H13" s="719"/>
       <c r="I13" s="24"/>
-      <c r="J13" s="680" t="s">
+      <c r="J13" s="718" t="s">
         <v>295</v>
       </c>
-      <c r="K13" s="677"/>
-      <c r="M13" s="680" t="s">
+      <c r="K13" s="719"/>
+      <c r="M13" s="718" t="s">
         <v>296</v>
       </c>
-      <c r="N13" s="677"/>
+      <c r="N13" s="719"/>
       <c r="O13" s="24"/>
-      <c r="P13" s="680" t="s">
+      <c r="P13" s="718" t="s">
         <v>297</v>
       </c>
-      <c r="Q13" s="677"/>
-      <c r="S13" s="680" t="s">
+      <c r="Q13" s="719"/>
+      <c r="S13" s="718" t="s">
         <v>298</v>
       </c>
-      <c r="T13" s="677"/>
+      <c r="T13" s="719"/>
       <c r="U13" s="24"/>
-      <c r="V13" s="680" t="s">
+      <c r="V13" s="718" t="s">
         <v>299</v>
       </c>
-      <c r="W13" s="677"/>
-      <c r="Y13" s="680" t="s">
+      <c r="W13" s="719"/>
+      <c r="Y13" s="718" t="s">
         <v>300</v>
       </c>
-      <c r="Z13" s="677"/>
+      <c r="Z13" s="719"/>
       <c r="AA13" s="24"/>
-      <c r="AB13" s="680" t="s">
+      <c r="AB13" s="718" t="s">
         <v>299</v>
       </c>
-      <c r="AC13" s="677"/>
+      <c r="AC13" s="719"/>
     </row>
     <row r="14" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A14" s="237" t="s">
@@ -30866,66 +30868,66 @@
       <c r="F16" s="24"/>
     </row>
     <row r="17" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A17" s="681" t="s">
+      <c r="A17" s="728" t="s">
         <v>304</v>
       </c>
-      <c r="B17" s="682"/>
-      <c r="C17" s="682"/>
-      <c r="D17" s="683"/>
+      <c r="B17" s="729"/>
+      <c r="C17" s="729"/>
+      <c r="D17" s="730"/>
       <c r="F17" s="24"/>
-      <c r="G17" s="681" t="s">
+      <c r="G17" s="728" t="s">
         <v>2</v>
       </c>
-      <c r="H17" s="682"/>
-      <c r="I17" s="682"/>
-      <c r="J17" s="683"/>
-      <c r="M17" s="681" t="s">
+      <c r="H17" s="729"/>
+      <c r="I17" s="729"/>
+      <c r="J17" s="730"/>
+      <c r="M17" s="728" t="s">
         <v>305</v>
       </c>
-      <c r="N17" s="682"/>
-      <c r="O17" s="682"/>
-      <c r="P17" s="683"/>
-      <c r="S17" s="681" t="s">
+      <c r="N17" s="729"/>
+      <c r="O17" s="729"/>
+      <c r="P17" s="730"/>
+      <c r="S17" s="728" t="s">
         <v>4</v>
       </c>
-      <c r="T17" s="682"/>
-      <c r="U17" s="682"/>
-      <c r="V17" s="683"/>
-      <c r="Y17" s="681" t="s">
+      <c r="T17" s="729"/>
+      <c r="U17" s="729"/>
+      <c r="V17" s="730"/>
+      <c r="Y17" s="728" t="s">
         <v>5</v>
       </c>
-      <c r="Z17" s="682"/>
-      <c r="AA17" s="682"/>
-      <c r="AB17" s="683"/>
+      <c r="Z17" s="729"/>
+      <c r="AA17" s="729"/>
+      <c r="AB17" s="730"/>
     </row>
     <row r="18" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A18" s="684"/>
-      <c r="B18" s="685"/>
-      <c r="C18" s="685"/>
-      <c r="D18" s="686"/>
+      <c r="A18" s="731"/>
+      <c r="B18" s="725"/>
+      <c r="C18" s="725"/>
+      <c r="D18" s="723"/>
       <c r="F18" s="24"/>
-      <c r="G18" s="684"/>
-      <c r="H18" s="685"/>
-      <c r="I18" s="685"/>
-      <c r="J18" s="686"/>
-      <c r="M18" s="684"/>
-      <c r="N18" s="685"/>
-      <c r="O18" s="685"/>
-      <c r="P18" s="686"/>
-      <c r="S18" s="684"/>
-      <c r="T18" s="685"/>
-      <c r="U18" s="685"/>
-      <c r="V18" s="686"/>
-      <c r="Y18" s="684"/>
-      <c r="Z18" s="685"/>
-      <c r="AA18" s="685"/>
-      <c r="AB18" s="686"/>
+      <c r="G18" s="731"/>
+      <c r="H18" s="725"/>
+      <c r="I18" s="725"/>
+      <c r="J18" s="723"/>
+      <c r="M18" s="731"/>
+      <c r="N18" s="725"/>
+      <c r="O18" s="725"/>
+      <c r="P18" s="723"/>
+      <c r="S18" s="731"/>
+      <c r="T18" s="725"/>
+      <c r="U18" s="725"/>
+      <c r="V18" s="723"/>
+      <c r="Y18" s="731"/>
+      <c r="Z18" s="725"/>
+      <c r="AA18" s="725"/>
+      <c r="AB18" s="723"/>
     </row>
     <row r="19" spans="1:28" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A19" s="676" t="s">
+      <c r="A19" s="736" t="s">
         <v>306</v>
       </c>
-      <c r="B19" s="677"/>
+      <c r="B19" s="719"/>
       <c r="C19" s="58" t="s">
         <v>307</v>
       </c>
@@ -30933,40 +30935,40 @@
         <v>308</v>
       </c>
       <c r="F19" s="24"/>
-      <c r="G19" s="676" t="s">
+      <c r="G19" s="736" t="s">
         <v>306</v>
       </c>
-      <c r="H19" s="677"/>
+      <c r="H19" s="719"/>
       <c r="I19" s="58" t="s">
         <v>307</v>
       </c>
       <c r="J19" s="58" t="s">
         <v>308</v>
       </c>
-      <c r="M19" s="676" t="s">
+      <c r="M19" s="736" t="s">
         <v>306</v>
       </c>
-      <c r="N19" s="677"/>
+      <c r="N19" s="719"/>
       <c r="O19" s="58" t="s">
         <v>307</v>
       </c>
       <c r="P19" s="58" t="s">
         <v>308</v>
       </c>
-      <c r="S19" s="676" t="s">
+      <c r="S19" s="736" t="s">
         <v>306</v>
       </c>
-      <c r="T19" s="677"/>
+      <c r="T19" s="719"/>
       <c r="U19" s="58" t="s">
         <v>307</v>
       </c>
       <c r="V19" s="58" t="s">
         <v>308</v>
       </c>
-      <c r="Y19" s="676" t="s">
+      <c r="Y19" s="736" t="s">
         <v>306</v>
       </c>
-      <c r="Z19" s="677"/>
+      <c r="Z19" s="719"/>
       <c r="AA19" s="58" t="s">
         <v>307</v>
       </c>
@@ -31325,12 +31327,12 @@
     <row r="29" spans="1:28" ht="13.2" x14ac:dyDescent="0.25"/>
     <row r="30" spans="1:28" ht="13.2" x14ac:dyDescent="0.25"/>
     <row r="31" spans="1:28" ht="22.8" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="693" t="s">
+      <c r="A31" s="737" t="s">
         <v>314</v>
       </c>
-      <c r="B31" s="694"/>
-      <c r="C31" s="694"/>
-      <c r="D31" s="694"/>
+      <c r="B31" s="721"/>
+      <c r="C31" s="721"/>
+      <c r="D31" s="721"/>
       <c r="G31" s="9"/>
       <c r="H31" s="9"/>
       <c r="I31" s="9"/>
@@ -31715,10 +31717,10 @@
       <c r="N49" s="9"/>
     </row>
     <row r="52" spans="1:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="689" t="s">
+      <c r="A52" s="732" t="s">
         <v>340</v>
       </c>
-      <c r="B52" s="690"/>
+      <c r="B52" s="733"/>
     </row>
     <row r="53" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A53" s="68" t="s">
@@ -31924,11 +31926,18 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="Y19:Z19"/>
+    <mergeCell ref="Y3:AA3"/>
+    <mergeCell ref="AB3:AC3"/>
+    <mergeCell ref="Y13:Z13"/>
+    <mergeCell ref="AB13:AC13"/>
+    <mergeCell ref="Y17:AB18"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="S3:U3"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="V13:W13"/>
+    <mergeCell ref="S17:V18"/>
     <mergeCell ref="M17:P18"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:K3"/>
@@ -31945,18 +31954,11 @@
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="S3:U3"/>
-    <mergeCell ref="V3:W3"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="V13:W13"/>
-    <mergeCell ref="S17:V18"/>
-    <mergeCell ref="Y19:Z19"/>
-    <mergeCell ref="Y3:AA3"/>
-    <mergeCell ref="AB3:AC3"/>
-    <mergeCell ref="Y13:Z13"/>
-    <mergeCell ref="AB13:AC13"/>
-    <mergeCell ref="Y17:AB18"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="M3:O3"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <legacyDrawing r:id="rId1"/>
@@ -31996,17 +31998,17 @@
       <c r="N1" s="24"/>
     </row>
     <row r="2" spans="1:15" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="A2" s="696" t="s">
+      <c r="A2" s="738" t="s">
         <v>345</v>
       </c>
-      <c r="B2" s="685"/>
-      <c r="C2" s="685"/>
-      <c r="D2" s="685"/>
-      <c r="E2" s="685"/>
-      <c r="F2" s="685"/>
-      <c r="G2" s="685"/>
-      <c r="H2" s="685"/>
-      <c r="I2" s="685"/>
+      <c r="B2" s="725"/>
+      <c r="C2" s="725"/>
+      <c r="D2" s="725"/>
+      <c r="E2" s="725"/>
+      <c r="F2" s="725"/>
+      <c r="G2" s="725"/>
+      <c r="H2" s="725"/>
+      <c r="I2" s="725"/>
       <c r="J2" s="238"/>
       <c r="K2" s="238"/>
       <c r="L2" s="238"/>
@@ -32804,6 +32806,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010096B3B8095E610F46997987F627BA2050" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b3bbc42fd73bed8b4972cfac315545d1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e7be84e2-caba-498a-9078-d8746d97147d" xmlns:ns3="364b9ec1-f1ed-4c2d-8f06-e465d44f7fe6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9231a099640da205526a21db75d4eba4" ns2:_="" ns3:_="">
     <xsd:import namespace="e7be84e2-caba-498a-9078-d8746d97147d"/>
@@ -33008,15 +33019,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC22CD36-AFB1-4957-9C99-E2B7FFF10FAB}">
   <ds:schemaRefs>
@@ -33029,6 +33031,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D143046-DCAF-400F-AAF8-4BBC718C1BD9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D29372E9-4A50-440A-97BA-AD99D95CD3C8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -33045,12 +33055,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D143046-DCAF-400F-AAF8-4BBC718C1BD9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Global Arriendos/informe Global ARRIENDOS_cor.xlsx
+++ b/Global Arriendos/informe Global ARRIENDOS_cor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\Portada Inmobiliaria\Inmuebles_Arrendados\Global Arriendos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B539AF0-ABB9-4D7D-B5C8-0E13F9F1CB36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEA749F0-76E7-4C31-9E53-E68F399C158E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7387,30 +7387,30 @@
     <xf numFmtId="0" fontId="3" fillId="19" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="26" fillId="21" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -30183,17 +30183,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="A1" s="720" t="s">
+      <c r="A1" s="737" t="s">
         <v>275</v>
       </c>
-      <c r="B1" s="721"/>
-      <c r="C1" s="721"/>
-      <c r="D1" s="721"/>
-      <c r="E1" s="721"/>
-      <c r="F1" s="721"/>
-      <c r="G1" s="721"/>
-      <c r="H1" s="721"/>
-      <c r="I1" s="721"/>
+      <c r="B1" s="736"/>
+      <c r="C1" s="736"/>
+      <c r="D1" s="736"/>
+      <c r="E1" s="736"/>
+      <c r="F1" s="736"/>
+      <c r="G1" s="736"/>
+      <c r="H1" s="736"/>
+      <c r="I1" s="736"/>
       <c r="J1" s="24"/>
     </row>
     <row r="2" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
@@ -30209,49 +30209,49 @@
       <c r="J2" s="24"/>
     </row>
     <row r="3" spans="1:30" ht="21" x14ac:dyDescent="0.4">
-      <c r="A3" s="724" t="s">
+      <c r="A3" s="729" t="s">
         <v>276</v>
       </c>
-      <c r="B3" s="725"/>
-      <c r="C3" s="723"/>
-      <c r="D3" s="722" t="s">
+      <c r="B3" s="727"/>
+      <c r="C3" s="728"/>
+      <c r="D3" s="730" t="s">
         <v>277</v>
       </c>
-      <c r="E3" s="723"/>
+      <c r="E3" s="728"/>
       <c r="F3" s="24"/>
-      <c r="G3" s="724" t="s">
+      <c r="G3" s="729" t="s">
         <v>278</v>
       </c>
-      <c r="H3" s="725"/>
-      <c r="I3" s="723"/>
-      <c r="J3" s="722" t="s">
+      <c r="H3" s="727"/>
+      <c r="I3" s="728"/>
+      <c r="J3" s="730" t="s">
         <v>279</v>
       </c>
-      <c r="K3" s="723"/>
-      <c r="M3" s="726" t="s">
+      <c r="K3" s="728"/>
+      <c r="M3" s="720" t="s">
         <v>280</v>
       </c>
-      <c r="N3" s="727"/>
+      <c r="N3" s="721"/>
       <c r="O3" s="719"/>
-      <c r="P3" s="726" t="s">
+      <c r="P3" s="720" t="s">
         <v>281</v>
       </c>
       <c r="Q3" s="719"/>
-      <c r="S3" s="726" t="s">
+      <c r="S3" s="720" t="s">
         <v>282</v>
       </c>
-      <c r="T3" s="727"/>
+      <c r="T3" s="721"/>
       <c r="U3" s="719"/>
-      <c r="V3" s="726" t="s">
+      <c r="V3" s="720" t="s">
         <v>283</v>
       </c>
       <c r="W3" s="719"/>
-      <c r="Y3" s="726" t="s">
+      <c r="Y3" s="720" t="s">
         <v>284</v>
       </c>
-      <c r="Z3" s="727"/>
+      <c r="Z3" s="721"/>
       <c r="AA3" s="719"/>
-      <c r="AB3" s="726" t="s">
+      <c r="AB3" s="720" t="s">
         <v>285</v>
       </c>
       <c r="AC3" s="719"/>
@@ -30749,49 +30749,49 @@
       <c r="F12" s="24"/>
     </row>
     <row r="13" spans="1:30" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A13" s="734" t="s">
+      <c r="A13" s="733" t="s">
         <v>292</v>
       </c>
       <c r="B13" s="719"/>
       <c r="C13" s="24"/>
-      <c r="D13" s="735" t="s">
+      <c r="D13" s="734" t="s">
         <v>293</v>
       </c>
-      <c r="E13" s="723"/>
+      <c r="E13" s="728"/>
       <c r="F13" s="24"/>
-      <c r="G13" s="734" t="s">
+      <c r="G13" s="733" t="s">
         <v>294</v>
       </c>
       <c r="H13" s="719"/>
       <c r="I13" s="24"/>
-      <c r="J13" s="718" t="s">
+      <c r="J13" s="722" t="s">
         <v>295</v>
       </c>
       <c r="K13" s="719"/>
-      <c r="M13" s="718" t="s">
+      <c r="M13" s="722" t="s">
         <v>296</v>
       </c>
       <c r="N13" s="719"/>
       <c r="O13" s="24"/>
-      <c r="P13" s="718" t="s">
+      <c r="P13" s="722" t="s">
         <v>297</v>
       </c>
       <c r="Q13" s="719"/>
-      <c r="S13" s="718" t="s">
+      <c r="S13" s="722" t="s">
         <v>298</v>
       </c>
       <c r="T13" s="719"/>
       <c r="U13" s="24"/>
-      <c r="V13" s="718" t="s">
+      <c r="V13" s="722" t="s">
         <v>299</v>
       </c>
       <c r="W13" s="719"/>
-      <c r="Y13" s="718" t="s">
+      <c r="Y13" s="722" t="s">
         <v>300</v>
       </c>
       <c r="Z13" s="719"/>
       <c r="AA13" s="24"/>
-      <c r="AB13" s="718" t="s">
+      <c r="AB13" s="722" t="s">
         <v>299</v>
       </c>
       <c r="AC13" s="719"/>
@@ -30868,63 +30868,63 @@
       <c r="F16" s="24"/>
     </row>
     <row r="17" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A17" s="728" t="s">
+      <c r="A17" s="723" t="s">
         <v>304</v>
       </c>
-      <c r="B17" s="729"/>
-      <c r="C17" s="729"/>
-      <c r="D17" s="730"/>
+      <c r="B17" s="724"/>
+      <c r="C17" s="724"/>
+      <c r="D17" s="725"/>
       <c r="F17" s="24"/>
-      <c r="G17" s="728" t="s">
+      <c r="G17" s="723" t="s">
         <v>2</v>
       </c>
-      <c r="H17" s="729"/>
-      <c r="I17" s="729"/>
-      <c r="J17" s="730"/>
-      <c r="M17" s="728" t="s">
+      <c r="H17" s="724"/>
+      <c r="I17" s="724"/>
+      <c r="J17" s="725"/>
+      <c r="M17" s="723" t="s">
         <v>305</v>
       </c>
-      <c r="N17" s="729"/>
-      <c r="O17" s="729"/>
-      <c r="P17" s="730"/>
-      <c r="S17" s="728" t="s">
+      <c r="N17" s="724"/>
+      <c r="O17" s="724"/>
+      <c r="P17" s="725"/>
+      <c r="S17" s="723" t="s">
         <v>4</v>
       </c>
-      <c r="T17" s="729"/>
-      <c r="U17" s="729"/>
-      <c r="V17" s="730"/>
-      <c r="Y17" s="728" t="s">
+      <c r="T17" s="724"/>
+      <c r="U17" s="724"/>
+      <c r="V17" s="725"/>
+      <c r="Y17" s="723" t="s">
         <v>5</v>
       </c>
-      <c r="Z17" s="729"/>
-      <c r="AA17" s="729"/>
-      <c r="AB17" s="730"/>
+      <c r="Z17" s="724"/>
+      <c r="AA17" s="724"/>
+      <c r="AB17" s="725"/>
     </row>
     <row r="18" spans="1:28" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A18" s="731"/>
-      <c r="B18" s="725"/>
-      <c r="C18" s="725"/>
-      <c r="D18" s="723"/>
+      <c r="A18" s="726"/>
+      <c r="B18" s="727"/>
+      <c r="C18" s="727"/>
+      <c r="D18" s="728"/>
       <c r="F18" s="24"/>
-      <c r="G18" s="731"/>
-      <c r="H18" s="725"/>
-      <c r="I18" s="725"/>
-      <c r="J18" s="723"/>
-      <c r="M18" s="731"/>
-      <c r="N18" s="725"/>
-      <c r="O18" s="725"/>
-      <c r="P18" s="723"/>
-      <c r="S18" s="731"/>
-      <c r="T18" s="725"/>
-      <c r="U18" s="725"/>
-      <c r="V18" s="723"/>
-      <c r="Y18" s="731"/>
-      <c r="Z18" s="725"/>
-      <c r="AA18" s="725"/>
-      <c r="AB18" s="723"/>
+      <c r="G18" s="726"/>
+      <c r="H18" s="727"/>
+      <c r="I18" s="727"/>
+      <c r="J18" s="728"/>
+      <c r="M18" s="726"/>
+      <c r="N18" s="727"/>
+      <c r="O18" s="727"/>
+      <c r="P18" s="728"/>
+      <c r="S18" s="726"/>
+      <c r="T18" s="727"/>
+      <c r="U18" s="727"/>
+      <c r="V18" s="728"/>
+      <c r="Y18" s="726"/>
+      <c r="Z18" s="727"/>
+      <c r="AA18" s="727"/>
+      <c r="AB18" s="728"/>
     </row>
     <row r="19" spans="1:28" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A19" s="736" t="s">
+      <c r="A19" s="718" t="s">
         <v>306</v>
       </c>
       <c r="B19" s="719"/>
@@ -30935,7 +30935,7 @@
         <v>308</v>
       </c>
       <c r="F19" s="24"/>
-      <c r="G19" s="736" t="s">
+      <c r="G19" s="718" t="s">
         <v>306</v>
       </c>
       <c r="H19" s="719"/>
@@ -30945,7 +30945,7 @@
       <c r="J19" s="58" t="s">
         <v>308</v>
       </c>
-      <c r="M19" s="736" t="s">
+      <c r="M19" s="718" t="s">
         <v>306</v>
       </c>
       <c r="N19" s="719"/>
@@ -30955,7 +30955,7 @@
       <c r="P19" s="58" t="s">
         <v>308</v>
       </c>
-      <c r="S19" s="736" t="s">
+      <c r="S19" s="718" t="s">
         <v>306</v>
       </c>
       <c r="T19" s="719"/>
@@ -30965,7 +30965,7 @@
       <c r="V19" s="58" t="s">
         <v>308</v>
       </c>
-      <c r="Y19" s="736" t="s">
+      <c r="Y19" s="718" t="s">
         <v>306</v>
       </c>
       <c r="Z19" s="719"/>
@@ -31327,12 +31327,12 @@
     <row r="29" spans="1:28" ht="13.2" x14ac:dyDescent="0.25"/>
     <row r="30" spans="1:28" ht="13.2" x14ac:dyDescent="0.25"/>
     <row r="31" spans="1:28" ht="22.8" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="737" t="s">
+      <c r="A31" s="735" t="s">
         <v>314</v>
       </c>
-      <c r="B31" s="721"/>
-      <c r="C31" s="721"/>
-      <c r="D31" s="721"/>
+      <c r="B31" s="736"/>
+      <c r="C31" s="736"/>
+      <c r="D31" s="736"/>
       <c r="G31" s="9"/>
       <c r="H31" s="9"/>
       <c r="I31" s="9"/>
@@ -31717,10 +31717,10 @@
       <c r="N49" s="9"/>
     </row>
     <row r="52" spans="1:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="732" t="s">
+      <c r="A52" s="731" t="s">
         <v>340</v>
       </c>
-      <c r="B52" s="733"/>
+      <c r="B52" s="732"/>
     </row>
     <row r="53" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A53" s="68" t="s">
@@ -31926,18 +31926,11 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="Y19:Z19"/>
-    <mergeCell ref="Y3:AA3"/>
-    <mergeCell ref="AB3:AC3"/>
-    <mergeCell ref="Y13:Z13"/>
-    <mergeCell ref="AB13:AC13"/>
-    <mergeCell ref="Y17:AB18"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="S3:U3"/>
-    <mergeCell ref="V3:W3"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="V13:W13"/>
-    <mergeCell ref="S17:V18"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="M3:O3"/>
     <mergeCell ref="M17:P18"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:K3"/>
@@ -31954,11 +31947,18 @@
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="S3:U3"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="V13:W13"/>
+    <mergeCell ref="S17:V18"/>
+    <mergeCell ref="Y19:Z19"/>
+    <mergeCell ref="Y3:AA3"/>
+    <mergeCell ref="AB3:AC3"/>
+    <mergeCell ref="Y13:Z13"/>
+    <mergeCell ref="AB13:AC13"/>
+    <mergeCell ref="Y17:AB18"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <legacyDrawing r:id="rId1"/>
@@ -32001,14 +32001,14 @@
       <c r="A2" s="738" t="s">
         <v>345</v>
       </c>
-      <c r="B2" s="725"/>
-      <c r="C2" s="725"/>
-      <c r="D2" s="725"/>
-      <c r="E2" s="725"/>
-      <c r="F2" s="725"/>
-      <c r="G2" s="725"/>
-      <c r="H2" s="725"/>
-      <c r="I2" s="725"/>
+      <c r="B2" s="727"/>
+      <c r="C2" s="727"/>
+      <c r="D2" s="727"/>
+      <c r="E2" s="727"/>
+      <c r="F2" s="727"/>
+      <c r="G2" s="727"/>
+      <c r="H2" s="727"/>
+      <c r="I2" s="727"/>
       <c r="J2" s="238"/>
       <c r="K2" s="238"/>
       <c r="L2" s="238"/>
@@ -32806,15 +32806,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010096B3B8095E610F46997987F627BA2050" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b3bbc42fd73bed8b4972cfac315545d1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e7be84e2-caba-498a-9078-d8746d97147d" xmlns:ns3="364b9ec1-f1ed-4c2d-8f06-e465d44f7fe6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9231a099640da205526a21db75d4eba4" ns2:_="" ns3:_="">
     <xsd:import namespace="e7be84e2-caba-498a-9078-d8746d97147d"/>
@@ -33019,6 +33010,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC22CD36-AFB1-4957-9C99-E2B7FFF10FAB}">
   <ds:schemaRefs>
@@ -33031,14 +33031,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D143046-DCAF-400F-AAF8-4BBC718C1BD9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D29372E9-4A50-440A-97BA-AD99D95CD3C8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -33055,4 +33047,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D143046-DCAF-400F-AAF8-4BBC718C1BD9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>